--- a/templates/HEADWAY_SCENARIOS_v1.0.xlsx
+++ b/templates/HEADWAY_SCENARIOS_v1.0.xlsx
@@ -560,7 +560,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3. Row 3 contains an illustrative example row (marked with ID 'EXAMPLE_*'). Replace or delete before production use.</t>
+          <t>3. Row 3 contains a minimal valid baseline network for demonstration purposes. You may modify or replace it with your own railway data. The example is designed to load without validation errors.</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -789,6 +789,21 @@
       </c>
       <c r="C3" s="10" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>SCN_ALT_01</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Alternative headway sensitivity with extended overlap</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/templates/HEADWAY_SCENARIOS_v1.0.xlsx
+++ b/templates/HEADWAY_SCENARIOS_v1.0.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="85" customWidth="1" min="1" max="1"/>
@@ -586,24 +586,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7. For multi-link signalling blocks or TVS sections, define spatial geometry intervals in the 'BlockGeometry' or 'TVSGeometry' worksheet with sequential numbering.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>WORKSHEET INVENTORY:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>• ScenarioDefinitions: Alternative scenario branches</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>• ScenarioDefinitions: Alternative scenario branches</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>• Overrides: Targeted parameter overrides for non-baseline scenarios</t>
         </is>

--- a/templates/HEADWAY_SCENARIOS_v1.0.xlsx
+++ b/templates/HEADWAY_SCENARIOS_v1.0.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="85" customWidth="1" min="1" max="1"/>
@@ -593,24 +593,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>8. DEFAULT_PERFORMANCE_FACTOR: Optional scenario-level default performance factor for analyses within this scenario (0.5 to 1.0). Default 1.0 if blank.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>WORKSHEET INVENTORY:</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>• ScenarioDefinitions: Alternative scenario branches</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>• ScenarioDefinitions: Alternative scenario branches</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>• Overrides: Targeted parameter overrides for non-baseline scenarios</t>
         </is>
@@ -741,12 +748,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -765,6 +773,11 @@
           <t>IS_BASELINE</t>
         </is>
       </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>DEFAULT_PERFORMANCE_FACTOR</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -782,6 +795,11 @@
           <t>(Optional)</t>
         </is>
       </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>(Optional)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -797,6 +815,9 @@
       <c r="C3" s="10" t="b">
         <v>1</v>
       </c>
+      <c r="D3" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -812,6 +833,7 @@
       <c r="C4" s="10" t="b">
         <v>0</v>
       </c>
+      <c r="D4" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
